--- a/Día 13-Crear un sistema de Atención de pacientes médicos/Planta+Docente.xlsx
+++ b/Día 13-Crear un sistema de Atención de pacientes médicos/Planta+Docente.xlsx
@@ -1,33 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Udemy\Propios\Excel\Prácticas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Día 13-Crear un sistema de Atención de pacientes médicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2088E1E3-18C1-4F94-BEB7-74A1302D36BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A62982-9D5F-49EF-9F68-F30BBE09D2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="24120" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base de datos" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>Nombre</t>
   </si>
@@ -147,18 +154,31 @@
   </si>
   <si>
     <t>Docente Investigador</t>
+  </si>
+  <si>
+    <t>Buscar por Matrícula</t>
+  </si>
+  <si>
+    <t>DGT 657</t>
+  </si>
+  <si>
+    <t>Buscar por teléfono</t>
+  </si>
+  <si>
+    <t>5 5 5 9 8 0 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -191,8 +211,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="18"/>
         <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -243,13 +279,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -273,14 +310,18 @@
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Moneda" xfId="4" builtinId="4"/>
     <cellStyle name="Moneda_Relacion de personal (base)" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Relacion de personal (base)" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -619,23 +660,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="12" customWidth="1"/>
     <col min="3" max="3" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.5703125" style="1" customWidth="1"/>
-    <col min="10" max="13" width="9.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="5" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.5546875" style="1" customWidth="1"/>
+    <col min="10" max="13" width="9.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>23</v>
       </c>
@@ -658,7 +699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>24</v>
       </c>
@@ -681,7 +722,7 @@
         <v>23702</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>25</v>
       </c>
@@ -704,7 +745,7 @@
         <v>23713</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
@@ -727,7 +768,7 @@
         <v>23767</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
@@ -750,7 +791,7 @@
         <v>24693</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>28</v>
       </c>
@@ -773,7 +814,7 @@
         <v>24704</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>29</v>
       </c>
@@ -796,7 +837,7 @@
         <v>13751</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>30</v>
       </c>
@@ -819,7 +860,7 @@
         <v>22554</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>31</v>
       </c>
@@ -842,7 +883,7 @@
         <v>22565</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>32</v>
       </c>
@@ -865,7 +906,7 @@
         <v>25443</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>33</v>
       </c>
@@ -888,7 +929,7 @@
         <v>14862</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>34</v>
       </c>
@@ -911,7 +952,7 @@
         <v>22971</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>35</v>
       </c>
@@ -934,7 +975,7 @@
         <v>22982</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>36</v>
       </c>
@@ -957,7 +998,7 @@
         <v>19334</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>37</v>
       </c>
@@ -980,16 +1021,64 @@
         <v>24038</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
     </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="12">
+        <f>VLOOKUP(SUBSTITUTE($A$18," ",""),$A$2:$G$15,2,FALSE)</f>
+        <v>5559804</v>
+      </c>
+      <c r="C18" s="12" t="str">
+        <f>VLOOKUP(SUBSTITUTE(SUBSTITUTE($A$18," ","")," ",""),$A$2:$G$15,3,FALSE)</f>
+        <v>Adriana Hoyos</v>
+      </c>
+      <c r="D18" s="12" t="str">
+        <f>VLOOKUP(SUBSTITUTE(SUBSTITUTE($A$18," ","")," ",""),$A$2:$G$15,4,FALSE)</f>
+        <v>Docente</v>
+      </c>
+      <c r="E18" s="16">
+        <f>VLOOKUP(SUBSTITUTE(SUBSTITUTE($A$18," ","")," ",""),$A$2:$G$15,5,FALSE)</f>
+        <v>2700000</v>
+      </c>
+      <c r="F18" s="9">
+        <f>VLOOKUP(SUBSTITUTE(SUBSTITUTE($A$18," ","")," ",""),$A$2:$G$15,6,FALSE)</f>
+        <v>31446</v>
+      </c>
+      <c r="G18" s="9">
+        <f>VLOOKUP(SUBSTITUTE(SUBSTITUTE($A$18," ","")," ",""),$A$2:$G$15,7,FALSE)</f>
+        <v>23702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f>VLOOKUP(_xlfn.NUMBERVALUE(SUBSTITUTE($B$21," ","")),$B$2:$G$15,2,FALSE)</f>
+        <v>Adriana Hoyos</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="C2:G15">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G15">
     <sortCondition ref="C2:C15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>